--- a/data/trans_dic/P19C04-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 16,67</t>
+          <t>9,55; 16,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 17,68</t>
+          <t>10,3; 18,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 12,34</t>
+          <t>6,34; 12,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,15</t>
+          <t>6,08; 10,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,66</t>
+          <t>4,29; 10,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 14,71</t>
+          <t>7,28; 15,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 11,07</t>
+          <t>5,16; 11,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,39</t>
+          <t>3,26; 6,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 13,36</t>
+          <t>8,23; 13,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 15,04</t>
+          <t>9,79; 15,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,81</t>
+          <t>6,24; 10,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,39</t>
+          <t>5,43; 8,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,68; 20,44</t>
+          <t>11,88; 20,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 18,66</t>
+          <t>11,36; 19,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 16,82</t>
+          <t>9,14; 17,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 13,38</t>
+          <t>7,57; 13,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 11,09</t>
+          <t>5,01; 11,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 14,49</t>
+          <t>7,41; 14,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,25</t>
+          <t>3,45; 8,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 8,21</t>
+          <t>4,0; 8,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 13,87</t>
+          <t>9,05; 14,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,9</t>
+          <t>10,37; 15,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 11,94</t>
+          <t>6,99; 11,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,11</t>
+          <t>6,58; 10,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,24; 25,14</t>
+          <t>17,77; 25,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,57; 30,29</t>
+          <t>22,66; 30,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,83; 22,03</t>
+          <t>14,53; 22,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 15,93</t>
+          <t>3,44; 16,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 20,3</t>
+          <t>8,7; 19,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,6</t>
+          <t>7,56; 16,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 23,28</t>
+          <t>9,95; 23,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 14,52</t>
+          <t>6,97; 14,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,96; 22,86</t>
+          <t>16,26; 23,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,74; 24,78</t>
+          <t>18,53; 24,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,49; 21,22</t>
+          <t>14,44; 20,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 14,55</t>
+          <t>3,84; 14,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,31; 28,39</t>
+          <t>22,3; 28,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,09; 35,6</t>
+          <t>29,23; 35,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,27; 24,44</t>
+          <t>18,61; 24,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,73; 20,89</t>
+          <t>16,15; 21,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,01; 19,13</t>
+          <t>13,29; 19,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,72; 18,64</t>
+          <t>12,67; 18,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 15,44</t>
+          <t>9,97; 15,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 11,32</t>
+          <t>4,25; 11,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,27; 23,51</t>
+          <t>19,51; 23,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,18; 27,5</t>
+          <t>23,07; 27,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,63; 19,42</t>
+          <t>15,5; 19,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 15,53</t>
+          <t>9,19; 15,58</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,14; 30,28</t>
+          <t>19,22; 30,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,62; 38,06</t>
+          <t>29,03; 38,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,35; 32,21</t>
+          <t>23,35; 32,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,76; 31,49</t>
+          <t>23,13; 31,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,45; 23,93</t>
+          <t>16,28; 24,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,48; 27,34</t>
+          <t>20,95; 27,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,57; 18,59</t>
+          <t>12,56; 19,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,73; 19,0</t>
+          <t>11,37; 18,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,52; 24,98</t>
+          <t>18,57; 24,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,9; 30,49</t>
+          <t>25,18; 30,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,19; 23,75</t>
+          <t>18,23; 23,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,19; 22,13</t>
+          <t>16,54; 22,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,05; 14,72</t>
+          <t>5,91; 14,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 14,28</t>
+          <t>6,11; 13,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,15; 13,5</t>
+          <t>6,24; 13,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 13,66</t>
+          <t>2,9; 13,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,95; 18,79</t>
+          <t>14,11; 18,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,03; 23,35</t>
+          <t>18,24; 23,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,8; 19,47</t>
+          <t>13,98; 19,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,31</t>
+          <t>11,18; 15,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,19; 17,17</t>
+          <t>13,14; 17,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,26; 21,14</t>
+          <t>16,57; 20,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,68; 17,13</t>
+          <t>12,6; 17,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,82; 13,93</t>
+          <t>10,01; 13,86</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,32; 21,59</t>
+          <t>18,37; 21,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,13; 26,39</t>
+          <t>23,08; 26,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 19,36</t>
+          <t>16,45; 19,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,48; 15,95</t>
+          <t>11,42; 16,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,44; 16,09</t>
+          <t>13,26; 15,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,23; 19,2</t>
+          <t>16,22; 18,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,85; 14,38</t>
+          <t>11,83; 14,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,52; 11,69</t>
+          <t>8,52; 11,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,16; 18,2</t>
+          <t>16,17; 18,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19,86; 22,11</t>
+          <t>20,0; 22,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,42; 16,49</t>
+          <t>14,44; 16,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 13,44</t>
+          <t>10,78; 13,51</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por la extracción de algún diente o muela (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36326; 64405</t>
+          <t>36895; 63957</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40664; 69878</t>
+          <t>40740; 71399</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24736; 47851</t>
+          <t>24580; 47609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31752; 55576</t>
+          <t>30329; 54686</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11717; 28592</t>
+          <t>11510; 28902</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20652; 43231</t>
+          <t>21410; 44333</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15791; 34953</t>
+          <t>16306; 34792</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14256; 28165</t>
+          <t>14373; 28515</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54403; 87455</t>
+          <t>53851; 86308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66575; 103647</t>
+          <t>67515; 104549</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45369; 76023</t>
+          <t>43896; 74755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50927; 78835</t>
+          <t>51039; 77793</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35075; 61374</t>
+          <t>35655; 60540</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42710; 71588</t>
+          <t>43593; 74484</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28967; 53260</t>
+          <t>28942; 54499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34416; 60008</t>
+          <t>33948; 60009</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16585; 36986</t>
+          <t>16726; 38387</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23140; 45412</t>
+          <t>23245; 45811</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12100; 30847</t>
+          <t>11523; 29846</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15223; 30999</t>
+          <t>15089; 30977</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54733; 87890</t>
+          <t>57365; 91192</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71082; 110843</t>
+          <t>72322; 110812</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46433; 77608</t>
+          <t>45438; 77299</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>55028; 83481</t>
+          <t>54321; 84113</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>74183; 108159</t>
+          <t>76460; 110263</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>120872; 162222</t>
+          <t>121322; 162313</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60110; 89257</t>
+          <t>58895; 89887</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20865; 105263</t>
+          <t>22701; 106188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11948; 28434</t>
+          <t>12180; 27691</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17270; 37380</t>
+          <t>18126; 38586</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13519; 32460</t>
+          <t>13876; 32739</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11944; 23961</t>
+          <t>11492; 24481</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>91020; 130367</t>
+          <t>92742; 131694</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145293; 192056</t>
+          <t>143651; 190546</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78900; 115571</t>
+          <t>78647; 114083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38098; 120131</t>
+          <t>31685; 120573</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>194416; 247436</t>
+          <t>194310; 246408</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>282939; 346259</t>
+          <t>284292; 346455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>160729; 214931</t>
+          <t>163704; 212217</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>157032; 208535</t>
+          <t>161159; 210437</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77578; 114070</t>
+          <t>79251; 115002</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88925; 130299</t>
+          <t>88548; 128259</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69327; 105433</t>
+          <t>68099; 103746</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41586; 108554</t>
+          <t>40768; 109269</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>282812; 345011</t>
+          <t>286361; 348190</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>387539; 459678</t>
+          <t>385587; 460639</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>244165; 303418</t>
+          <t>242213; 305247</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>188524; 304001</t>
+          <t>179788; 304944</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>47462; 75067</t>
+          <t>47647; 76333</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>115422; 153519</t>
+          <t>117077; 155872</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99268; 136944</t>
+          <t>99276; 138041</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99877; 138203</t>
+          <t>101485; 138456</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>75028; 109157</t>
+          <t>74254; 110131</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>136952; 182829</t>
+          <t>140111; 184568</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70080; 103639</t>
+          <t>70026; 106544</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95520; 154625</t>
+          <t>92544; 150808</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>130395; 175838</t>
+          <t>130768; 174200</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>266926; 326869</t>
+          <t>269972; 326092</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>178706; 233363</t>
+          <t>179105; 231259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>202832; 277260</t>
+          <t>207188; 280441</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12840; 31231</t>
+          <t>12554; 30376</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13747; 31581</t>
+          <t>13505; 30489</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14860; 32605</t>
+          <t>15078; 32664</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7159; 31698</t>
+          <t>6730; 32322</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>131956; 177667</t>
+          <t>133400; 176658</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>166992; 216320</t>
+          <t>168929; 217917</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>113885; 160723</t>
+          <t>115360; 160839</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84022; 113867</t>
+          <t>83174; 112806</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>152743; 198838</t>
+          <t>152195; 199572</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>186616; 242580</t>
+          <t>190138; 239873</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>135223; 182712</t>
+          <t>134473; 182716</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>95874; 135936</t>
+          <t>97691; 135262</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>448647; 528703</t>
+          <t>449655; 530314</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>673432; 768474</t>
+          <t>671919; 771843</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>434163; 514160</t>
+          <t>436941; 515877</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>343308; 522622</t>
+          <t>374078; 524262</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>368158; 440775</t>
+          <t>363243; 436091</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>509779; 603101</t>
+          <t>509463; 594915</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>338231; 410445</t>
+          <t>337750; 413760</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>298379; 409136</t>
+          <t>298303; 408664</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>838187; 944199</t>
+          <t>838981; 952127</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1201974; 1338228</t>
+          <t>1210570; 1337341</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>794422; 908645</t>
+          <t>795535; 906355</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>726195; 911152</t>
+          <t>730355; 915276</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C04-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19C04-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,55; 16,56</t>
+          <t>9,72; 16,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,3; 18,06</t>
+          <t>9,99; 17,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,28</t>
+          <t>6,22; 12,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,97</t>
+          <t>6,23; 10,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,77</t>
+          <t>4,46; 11,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,08</t>
+          <t>7,22; 15,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 11,02</t>
+          <t>4,9; 11,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,47</t>
+          <t>3,27; 6,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,19</t>
+          <t>8,1; 12,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 15,17</t>
+          <t>9,7; 15,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,63</t>
+          <t>6,49; 10,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,28</t>
+          <t>5,28; 8,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,88; 20,17</t>
+          <t>11,5; 20,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,36; 19,41</t>
+          <t>11,02; 18,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 17,21</t>
+          <t>8,99; 17,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 13,38</t>
+          <t>7,59; 13,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 11,51</t>
+          <t>4,83; 11,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 14,61</t>
+          <t>7,73; 15,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,95</t>
+          <t>3,54; 9,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,2</t>
+          <t>4,21; 8,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 14,39</t>
+          <t>8,91; 14,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,37; 15,89</t>
+          <t>10,32; 15,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,89</t>
+          <t>7,07; 11,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 10,18</t>
+          <t>6,54; 9,97</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,77; 25,63</t>
+          <t>17,74; 25,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,66; 30,31</t>
+          <t>22,58; 30,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,53; 22,18</t>
+          <t>14,48; 21,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 16,07</t>
+          <t>12,31; 19,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 19,77</t>
+          <t>8,77; 20,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,56; 16,1</t>
+          <t>7,43; 15,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,95; 23,48</t>
+          <t>9,71; 23,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 14,84</t>
+          <t>7,31; 14,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,26; 23,09</t>
+          <t>16,15; 22,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,53; 24,58</t>
+          <t>18,72; 24,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,44; 20,95</t>
+          <t>14,36; 21,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 14,6</t>
+          <t>11,75; 16,99</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,3; 28,28</t>
+          <t>22,41; 28,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,23; 35,62</t>
+          <t>29,42; 35,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,61; 24,13</t>
+          <t>18,66; 23,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,15; 21,08</t>
+          <t>16,73; 21,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,29; 19,29</t>
+          <t>13,13; 19,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,67; 18,35</t>
+          <t>12,78; 18,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 15,19</t>
+          <t>10,09; 15,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,4</t>
+          <t>9,22; 12,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,51; 23,72</t>
+          <t>19,52; 23,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,07; 27,56</t>
+          <t>23,17; 27,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,5; 19,54</t>
+          <t>15,5; 19,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 15,58</t>
+          <t>13,92; 17,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,22; 30,79</t>
+          <t>18,88; 29,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,03; 38,65</t>
+          <t>28,93; 38,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,35; 32,47</t>
+          <t>23,32; 31,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23,13; 31,55</t>
+          <t>25,28; 33,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,28; 24,15</t>
+          <t>16,68; 23,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,95; 27,6</t>
+          <t>20,7; 27,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,56; 19,11</t>
+          <t>12,52; 18,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 18,53</t>
+          <t>15,76; 19,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,57; 24,74</t>
+          <t>18,52; 24,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,18; 30,42</t>
+          <t>24,85; 30,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,23; 23,53</t>
+          <t>18,23; 23,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,54; 22,38</t>
+          <t>20,37; 24,59</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,91; 14,31</t>
+          <t>6,19; 14,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,11; 13,78</t>
+          <t>6,34; 13,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,52</t>
+          <t>5,97; 13,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,9; 13,92</t>
+          <t>3,42; 14,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,11; 18,68</t>
+          <t>13,94; 18,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,24; 23,52</t>
+          <t>18,23; 23,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,98; 19,49</t>
+          <t>13,64; 19,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,18; 15,16</t>
+          <t>11,22; 15,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,14; 17,24</t>
+          <t>12,9; 16,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,57; 20,9</t>
+          <t>16,42; 20,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,6; 17,13</t>
+          <t>12,74; 17,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,01; 13,86</t>
+          <t>9,96; 13,92</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,37; 21,66</t>
+          <t>18,41; 21,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,08; 26,51</t>
+          <t>23,14; 26,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,45; 19,43</t>
+          <t>16,48; 19,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,42; 16,0</t>
+          <t>14,98; 17,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,26; 15,92</t>
+          <t>13,5; 16,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,22; 18,94</t>
+          <t>16,32; 18,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,83; 14,49</t>
+          <t>11,81; 14,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,52; 11,68</t>
+          <t>10,61; 12,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,17; 18,35</t>
+          <t>16,17; 18,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,0; 22,09</t>
+          <t>19,96; 22,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,44; 16,45</t>
+          <t>14,36; 16,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,78; 13,51</t>
+          <t>13,0; 14,61</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41913</t>
+          <t>45624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62794</t>
+          <t>68064</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36895; 63957</t>
+          <t>37555; 63212</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40740; 71399</t>
+          <t>39487; 69971</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24580; 47609</t>
+          <t>24110; 47616</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30329; 54686</t>
+          <t>33697; 59393</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11510; 28902</t>
+          <t>11977; 29690</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21410; 44333</t>
+          <t>21229; 45131</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16306; 34792</t>
+          <t>15468; 34836</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14373; 28515</t>
+          <t>15757; 30817</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53851; 86308</t>
+          <t>53005; 84615</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67515; 104549</t>
+          <t>66867; 103553</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43896; 74755</t>
+          <t>45637; 76438</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51039; 77793</t>
+          <t>53987; 84592</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45814</t>
+          <t>48458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67636</t>
+          <t>72928</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35655; 60540</t>
+          <t>34525; 60814</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43593; 74484</t>
+          <t>42271; 71126</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28942; 54499</t>
+          <t>28482; 54042</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33948; 60009</t>
+          <t>36401; 64142</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16726; 38387</t>
+          <t>16100; 36849</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23245; 45811</t>
+          <t>24237; 47866</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11523; 29846</t>
+          <t>11801; 31295</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15089; 30977</t>
+          <t>17609; 34940</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57365; 91192</t>
+          <t>56458; 89237</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72322; 110812</t>
+          <t>71967; 108175</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45438; 77299</t>
+          <t>45984; 77188</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54321; 84113</t>
+          <t>58694; 89449</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62681</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79892</t>
+          <t>92220</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76460; 110263</t>
+          <t>76311; 110050</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>121322; 162313</t>
+          <t>120924; 162110</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58895; 89887</t>
+          <t>58667; 88960</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22701; 106188</t>
+          <t>57094; 89562</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12180; 27691</t>
+          <t>12278; 28169</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18126; 38586</t>
+          <t>17802; 38066</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13876; 32739</t>
+          <t>13535; 33408</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11492; 24481</t>
+          <t>13508; 26807</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>92742; 131694</t>
+          <t>92135; 129375</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143651; 190546</t>
+          <t>145131; 192882</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78647; 114083</t>
+          <t>78194; 115377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31685; 120573</t>
+          <t>76190; 110189</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182376</t>
+          <t>207364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80423</t>
+          <t>91117</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>262799</t>
+          <t>298481</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>194310; 246408</t>
+          <t>195334; 248207</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>284292; 346455</t>
+          <t>286155; 346495</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>163704; 212217</t>
+          <t>164103; 210838</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>161159; 210437</t>
+          <t>183274; 235408</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>79251; 115002</t>
+          <t>78309; 114499</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88548; 128259</t>
+          <t>89307; 128677</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68099; 103746</t>
+          <t>68909; 103944</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40768; 109269</t>
+          <t>77111; 106793</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>286361; 348190</t>
+          <t>286485; 347979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>385587; 460639</t>
+          <t>387257; 458643</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>242213; 305247</t>
+          <t>242201; 302684</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>179788; 304944</t>
+          <t>269054; 331239</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118644</t>
+          <t>147869</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>129762</t>
+          <t>141802</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>248406</t>
+          <t>289670</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>47647; 76333</t>
+          <t>46797; 73115</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>117077; 155872</t>
+          <t>116688; 154374</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>99276; 138041</t>
+          <t>99169; 135610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101485; 138456</t>
+          <t>128880; 171045</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>74254; 110131</t>
+          <t>76055; 108859</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>140111; 184568</t>
+          <t>138458; 182721</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70026; 106544</t>
+          <t>69803; 103771</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>92544; 150808</t>
+          <t>125094; 157682</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>130768; 174200</t>
+          <t>130394; 173593</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>269972; 326092</t>
+          <t>266371; 326014</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>179105; 231259</t>
+          <t>179137; 229234</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>207188; 280441</t>
+          <t>265473; 320530</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>98290</t>
+          <t>106900</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>114426</t>
+          <t>122964</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12554; 30376</t>
+          <t>13139; 31712</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13505; 30489</t>
+          <t>14026; 30691</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15078; 32664</t>
+          <t>14430; 32883</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6730; 32322</t>
+          <t>7690; 32115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>133400; 176658</t>
+          <t>131779; 174498</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>168929; 217917</t>
+          <t>168877; 217128</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>115360; 160839</t>
+          <t>112562; 158031</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83174; 112806</t>
+          <t>91863; 124788</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>152195; 199572</t>
+          <t>149376; 196009</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>190138; 239873</t>
+          <t>188467; 238837</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>134473; 182716</t>
+          <t>135890; 183967</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>97691; 135262</t>
+          <t>103924; 145216</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>467564</t>
+          <t>538351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>368389</t>
+          <t>405976</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>835953</t>
+          <t>944327</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>449655; 530314</t>
+          <t>450707; 531133</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>671919; 771843</t>
+          <t>673751; 770563</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>436941; 515877</t>
+          <t>437729; 518628</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>374078; 524262</t>
+          <t>496477; 584016</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>363243; 436091</t>
+          <t>369894; 444588</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>509463; 594915</t>
+          <t>512519; 594991</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>337750; 413760</t>
+          <t>337152; 418827</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>298303; 408664</t>
+          <t>374831; 434444</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>838981; 952127</t>
+          <t>839142; 948703</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1210570; 1337341</t>
+          <t>1208281; 1336361</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>795535; 906355</t>
+          <t>791357; 903800</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>730355; 915276</t>
+          <t>890507; 1000418</t>
         </is>
       </c>
     </row>
